--- a/src/process_exp_result/processed_result/processed/result_split_processed.xlsx
+++ b/src/process_exp_result/processed_result/processed/result_split_processed.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yanzhang\Desktop\GeneLLM\src\process_exp_result\processed_result\processed\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072AAD82-A5BD-4524-B3BE-A689BBE0BA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-25710" yWindow="-70" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -286,12 +292,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -299,8 +305,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -346,17 +359,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -394,7 +415,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -428,6 +449,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -462,9 +484,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -637,11 +660,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="88" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="87" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,7 +692,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -672,16 +703,16 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>0.9017823947512302</v>
+        <v>0.90178239475123023</v>
       </c>
       <c r="E2" t="s">
         <v>63</v>
       </c>
       <c r="F2">
-        <v>0.8036300073219174</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0.80363000732191736</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -692,16 +723,16 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>0.7721262100893087</v>
+        <v>0.77212621008930871</v>
       </c>
       <c r="E3" t="s">
         <v>64</v>
       </c>
       <c r="F3">
-        <v>0.549390636366246</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>0.54939063636624597</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -712,16 +743,16 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>0.8039429896561018</v>
+        <v>0.80394298965610178</v>
       </c>
       <c r="E4" t="s">
         <v>65</v>
       </c>
       <c r="F4">
-        <v>0.6142441351238797</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>0.61424413512387965</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -732,16 +763,16 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>0.754447430625263</v>
+        <v>0.75444743062526298</v>
       </c>
       <c r="E5" t="s">
         <v>66</v>
       </c>
       <c r="F5">
-        <v>0.5102018867329589</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>0.51020188673295885</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -752,16 +783,16 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>0.6751513111317795</v>
+        <v>0.67515131113177951</v>
       </c>
       <c r="E6" t="s">
         <v>67</v>
       </c>
       <c r="F6">
-        <v>0.3511584613667778</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>0.35115846136677781</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -772,16 +803,16 @@
         <v>42</v>
       </c>
       <c r="D7">
-        <v>0.7050652792738848</v>
+        <v>0.70506527927388485</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7">
-        <v>0.4125100164267843</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>0.41251001642678431</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -792,16 +823,16 @@
         <v>43</v>
       </c>
       <c r="D8">
-        <v>0.8343742422960211</v>
+        <v>0.83437424229602108</v>
       </c>
       <c r="E8" t="s">
         <v>69</v>
       </c>
       <c r="F8">
-        <v>0.6715487281976388</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>0.67154872819763878</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -812,16 +843,16 @@
         <v>44</v>
       </c>
       <c r="D9">
-        <v>0.7941286804110712</v>
+        <v>0.79412868041107121</v>
       </c>
       <c r="E9" t="s">
         <v>70</v>
       </c>
       <c r="F9">
-        <v>0.5885947794510341</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>0.58859477945103411</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -832,16 +863,16 @@
         <v>45</v>
       </c>
       <c r="D10">
-        <v>0.9088902799827674</v>
+        <v>0.90889027998276739</v>
       </c>
       <c r="E10" t="s">
         <v>71</v>
       </c>
       <c r="F10">
-        <v>0.8180343050353981</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>0.81803430503539809</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -852,16 +883,16 @@
         <v>46</v>
       </c>
       <c r="D11">
-        <v>0.7477117179243916</v>
+        <v>0.74771171792439162</v>
       </c>
       <c r="E11" t="s">
         <v>72</v>
       </c>
       <c r="F11">
-        <v>0.5058748082468316</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>0.50587480824683162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -872,16 +903,16 @@
         <v>47</v>
       </c>
       <c r="D12">
-        <v>0.8196827294295594</v>
+        <v>0.81968272942955944</v>
       </c>
       <c r="E12" t="s">
         <v>73</v>
       </c>
       <c r="F12">
-        <v>0.6400058084599857</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>0.64000580845998567</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -892,16 +923,16 @@
         <v>48</v>
       </c>
       <c r="D13">
-        <v>0.9279460553879462</v>
+        <v>0.92794605538794617</v>
       </c>
       <c r="E13" t="s">
         <v>74</v>
       </c>
       <c r="F13">
-        <v>0.8559473473535611</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>0.85594734735356115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -912,16 +943,16 @@
         <v>49</v>
       </c>
       <c r="D14">
-        <v>0.9207317073170732</v>
+        <v>0.92073170731707321</v>
       </c>
       <c r="E14" t="s">
         <v>75</v>
       </c>
       <c r="F14">
-        <v>0.8414634146341463</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>0.84146341463414631</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -932,16 +963,16 @@
         <v>50</v>
       </c>
       <c r="D15">
-        <v>0.8953681814201908</v>
+        <v>0.89536818142019081</v>
       </c>
       <c r="E15" t="s">
         <v>76</v>
       </c>
       <c r="F15">
-        <v>0.7988010081336674</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>0.79880100813366739</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -952,16 +983,16 @@
         <v>51</v>
       </c>
       <c r="D16">
-        <v>0.7571572534275431</v>
+        <v>0.75715725342754314</v>
       </c>
       <c r="E16" t="s">
         <v>77</v>
       </c>
       <c r="F16">
-        <v>0.5152594763435192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>0.51525947634351921</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -972,16 +1003,16 @@
         <v>52</v>
       </c>
       <c r="D17">
-        <v>0.9728644063993028</v>
+        <v>0.97286440639930283</v>
       </c>
       <c r="E17" t="s">
         <v>78</v>
       </c>
       <c r="F17">
-        <v>0.9457465008165196</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>0.94574650081651956</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -998,10 +1029,10 @@
         <v>79</v>
       </c>
       <c r="F18">
-        <v>0.665155948677957</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>0.66515594867795702</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1012,16 +1043,16 @@
         <v>54</v>
       </c>
       <c r="D19">
-        <v>0.846010042794729</v>
+        <v>0.84601004279472902</v>
       </c>
       <c r="E19" t="s">
         <v>80</v>
       </c>
       <c r="F19">
-        <v>0.6926093987882067</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>0.69260939878820671</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1032,7 +1063,7 @@
         <v>55</v>
       </c>
       <c r="D20">
-        <v>0.882544548764131</v>
+        <v>0.88254454876413102</v>
       </c>
       <c r="E20" t="s">
         <v>81</v>
@@ -1041,7 +1072,7 @@
         <v>0.7651642574494969</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1052,16 +1083,16 @@
         <v>56</v>
       </c>
       <c r="D21">
-        <v>0.9185520869524821</v>
+        <v>0.91855208695248214</v>
       </c>
       <c r="E21" t="s">
         <v>82</v>
       </c>
       <c r="F21">
-        <v>0.8692047978899968</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>0.86920479788999683</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1072,7 +1103,7 @@
         <v>57</v>
       </c>
       <c r="D22">
-        <v>0.848956348384683</v>
+        <v>0.84895634838468303</v>
       </c>
       <c r="E22" t="s">
         <v>83</v>
@@ -1081,7 +1112,7 @@
         <v>0.6984037941232496</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -1098,10 +1129,10 @@
         <v>84</v>
       </c>
       <c r="F23">
-        <v>0.7565478037983465</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>0.75654780379834652</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1112,16 +1143,16 @@
         <v>59</v>
       </c>
       <c r="D24">
-        <v>0.8319455503583162</v>
+        <v>0.83194555035831619</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
       </c>
       <c r="F24">
-        <v>0.6644306906765791</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>0.66443069067657912</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -1132,16 +1163,16 @@
         <v>60</v>
       </c>
       <c r="D25">
-        <v>0.8039050900635908</v>
+        <v>0.80390509006359079</v>
       </c>
       <c r="E25" t="s">
         <v>86</v>
       </c>
       <c r="F25">
-        <v>0.6085893999469273</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>0.60858939994692729</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -1152,16 +1183,16 @@
         <v>61</v>
       </c>
       <c r="D26">
-        <v>0.8848248185490131</v>
+        <v>0.88482481854901307</v>
       </c>
       <c r="E26" t="s">
         <v>87</v>
       </c>
       <c r="F26">
-        <v>0.7723530825761357</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>0.77235308257613566</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1172,16 +1203,17 @@
         <v>62</v>
       </c>
       <c r="D27">
-        <v>0.7040492498881339</v>
+        <v>0.70404924988813389</v>
       </c>
       <c r="E27" t="s">
         <v>88</v>
       </c>
       <c r="F27">
-        <v>0.6663576519312082</v>
+        <v>0.66635765193120822</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>